--- a/libertadores/datasets_liberta/times_3o_e_4o_lugar_fase_2.xlsx
+++ b/libertadores/datasets_liberta/times_3o_e_4o_lugar_fase_2.xlsx
@@ -14,12 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Origem</t>
   </si>
   <si>
     <t>Grupo</t>
+  </si>
+  <si>
+    <t>ID do Time</t>
   </si>
   <si>
     <t>Nome do Time</t>
@@ -446,10 +449,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,284 +486,311 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>19033717</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <v>901.029296875</v>
+      </c>
+      <c r="J2">
+        <v>457.880029296875</v>
+      </c>
+      <c r="K2">
+        <v>443.149267578125</v>
+      </c>
+      <c r="L2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>1747619</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>882.379541015625</v>
+      </c>
+      <c r="J3">
+        <v>468.000048828125</v>
+      </c>
+      <c r="K3">
+        <v>414.3794921875</v>
+      </c>
+      <c r="L3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>117598</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>849.749951171875</v>
+      </c>
+      <c r="J4">
+        <v>469.270068359375</v>
+      </c>
+      <c r="K4">
+        <v>380.4798828125</v>
+      </c>
+      <c r="L4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>212042</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>870.180126953125</v>
+      </c>
+      <c r="J5">
+        <v>475.550146484375</v>
+      </c>
+      <c r="K5">
+        <v>394.62998046875</v>
+      </c>
+      <c r="L5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6">
+        <v>47544767</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>928.759375</v>
+      </c>
+      <c r="J6">
+        <v>475.4896484375</v>
+      </c>
+      <c r="K6">
+        <v>453.2697265625</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>387186</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>893.059326171875</v>
+      </c>
+      <c r="J7">
+        <v>490.409912109375</v>
+      </c>
+      <c r="K7">
+        <v>402.6494140625</v>
+      </c>
+      <c r="L7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="D2">
-        <v>9</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-      <c r="F2">
+      <c r="C8">
+        <v>1273719</v>
+      </c>
+      <c r="D8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2">
-        <v>846.21923828125</v>
-      </c>
-      <c r="I2">
-        <v>457.880029296875</v>
-      </c>
-      <c r="J2">
-        <v>388.339208984375</v>
-      </c>
-      <c r="K2">
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>969.950283203125</v>
+      </c>
+      <c r="J8">
+        <v>522.62021484375</v>
+      </c>
+      <c r="K8">
+        <v>447.330068359375</v>
+      </c>
+      <c r="L8">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-      <c r="F3">
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>36359</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+      <c r="G9">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3">
-        <v>820.36953125</v>
-      </c>
-      <c r="I3">
-        <v>468.000048828125</v>
-      </c>
-      <c r="J3">
-        <v>352.369482421875</v>
-      </c>
-      <c r="K3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>6</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-      <c r="H4">
-        <v>780.950146484375</v>
-      </c>
-      <c r="I4">
-        <v>469.270068359375</v>
-      </c>
-      <c r="J4">
-        <v>311.680078125</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-      <c r="H5">
-        <v>807.260205078125</v>
-      </c>
-      <c r="I5">
-        <v>475.550146484375</v>
-      </c>
-      <c r="J5">
-        <v>331.71005859375</v>
-      </c>
-      <c r="K5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="H6">
-        <v>859.339453125</v>
-      </c>
-      <c r="I6">
-        <v>475.4896484375</v>
-      </c>
-      <c r="J6">
-        <v>383.8498046875</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>6</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>825.869384765625</v>
-      </c>
-      <c r="I7">
-        <v>490.409912109375</v>
-      </c>
-      <c r="J7">
-        <v>335.45947265625</v>
-      </c>
-      <c r="K7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
-      <c r="H8">
-        <v>886.950283203125</v>
-      </c>
-      <c r="I8">
-        <v>522.62021484375</v>
-      </c>
-      <c r="J8">
-        <v>364.330068359375</v>
-      </c>
-      <c r="K8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>6</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
       <c r="H9">
-        <v>869.47951171875</v>
+        <v>4</v>
       </c>
       <c r="I9">
+        <v>935.3696484375</v>
+      </c>
+      <c r="J9">
         <v>451.849951171875</v>
       </c>
-      <c r="J9">
-        <v>417.629560546875</v>
-      </c>
       <c r="K9">
+        <v>483.519697265625</v>
+      </c>
+      <c r="L9">
         <v>4</v>
       </c>
     </row>

--- a/libertadores/datasets_liberta/times_3o_e_4o_lugar_fase_2.xlsx
+++ b/libertadores/datasets_liberta/times_3o_e_4o_lugar_fase_2.xlsx
@@ -88,10 +88,10 @@
     <t>DM Studio</t>
   </si>
   <si>
+    <t>Tabajara de Inhaua PB1</t>
+  </si>
+  <si>
     <t>Texas Club 2026</t>
-  </si>
-  <si>
-    <t>KillerColorado</t>
   </si>
 </sst>
 </file>
@@ -519,10 +519,10 @@
         <v>901.029296875</v>
       </c>
       <c r="J2">
-        <v>457.880029296875</v>
+        <v>457.880126953125</v>
       </c>
       <c r="K2">
-        <v>443.149267578125</v>
+        <v>443.149169921875</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -554,13 +554,13 @@
         <v>3</v>
       </c>
       <c r="I3">
-        <v>882.379541015625</v>
+        <v>882.379638671875</v>
       </c>
       <c r="J3">
-        <v>468.000048828125</v>
+        <v>468.000244140625</v>
       </c>
       <c r="K3">
-        <v>414.3794921875</v>
+        <v>414.37939453125</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -592,13 +592,13 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <v>849.749951171875</v>
+        <v>849.749755859375</v>
       </c>
       <c r="J4">
-        <v>469.270068359375</v>
+        <v>469.270263671875</v>
       </c>
       <c r="K4">
-        <v>380.4798828125</v>
+        <v>380.4794921875</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -630,13 +630,13 @@
         <v>5</v>
       </c>
       <c r="I5">
-        <v>870.180126953125</v>
+        <v>870.18017578125</v>
       </c>
       <c r="J5">
-        <v>475.550146484375</v>
+        <v>475.550048828125</v>
       </c>
       <c r="K5">
-        <v>394.62998046875</v>
+        <v>394.630126953125</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -668,13 +668,13 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>928.759375</v>
+        <v>928.75927734375</v>
       </c>
       <c r="J6">
-        <v>475.4896484375</v>
+        <v>475.48974609375</v>
       </c>
       <c r="K6">
-        <v>453.2697265625</v>
+        <v>453.26953125</v>
       </c>
       <c r="L6">
         <v>3</v>
@@ -726,31 +726,31 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>1273719</v>
+        <v>28741323</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I8">
-        <v>969.950283203125</v>
+        <v>887.879638671875</v>
       </c>
       <c r="J8">
-        <v>522.62021484375</v>
+        <v>498.380126953125</v>
       </c>
       <c r="K8">
-        <v>447.330068359375</v>
+        <v>389.49951171875</v>
       </c>
       <c r="L8">
         <v>3</v>
@@ -764,7 +764,7 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>36359</v>
+        <v>1273719</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
@@ -782,13 +782,13 @@
         <v>4</v>
       </c>
       <c r="I9">
-        <v>935.3696484375</v>
+        <v>969.950439453125</v>
       </c>
       <c r="J9">
-        <v>451.849951171875</v>
+        <v>522.6201171875</v>
       </c>
       <c r="K9">
-        <v>483.519697265625</v>
+        <v>447.330322265625</v>
       </c>
       <c r="L9">
         <v>4</v>

--- a/libertadores/datasets_liberta/times_3o_e_4o_lugar_fase_2.xlsx
+++ b/libertadores/datasets_liberta/times_3o_e_4o_lugar_fase_2.xlsx
@@ -88,10 +88,10 @@
     <t>DM Studio</t>
   </si>
   <si>
-    <t>Tabajara de Inhaua PB1</t>
-  </si>
-  <si>
     <t>Texas Club 2026</t>
+  </si>
+  <si>
+    <t>KillerColorado</t>
   </si>
 </sst>
 </file>
@@ -726,31 +726,31 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>28741323</v>
+        <v>1273719</v>
       </c>
       <c r="D8" t="s">
         <v>24</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>887.879638671875</v>
+        <v>969.950439453125</v>
       </c>
       <c r="J8">
-        <v>498.380126953125</v>
+        <v>522.6201171875</v>
       </c>
       <c r="K8">
-        <v>389.49951171875</v>
+        <v>447.330322265625</v>
       </c>
       <c r="L8">
         <v>3</v>
@@ -764,7 +764,7 @@
         <v>17</v>
       </c>
       <c r="C9">
-        <v>1273719</v>
+        <v>36359</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
@@ -782,13 +782,13 @@
         <v>4</v>
       </c>
       <c r="I9">
-        <v>969.950439453125</v>
+        <v>935.36962890625</v>
       </c>
       <c r="J9">
-        <v>522.6201171875</v>
+        <v>451.849853515625</v>
       </c>
       <c r="K9">
-        <v>447.330322265625</v>
+        <v>483.519775390625</v>
       </c>
       <c r="L9">
         <v>4</v>
